--- a/outputs/reports/rapport_ventes_latest.xlsx
+++ b/outputs/reports/rapport_ventes_latest.xlsx
@@ -467,7 +467,7 @@
                   <c:v>85838.85000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>93670.15000000001</c:v>
+                  <c:v>93670.14999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -890,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>46132.41578682303</v>
+        <v>46132.58927450875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1001,10 +1001,10 @@
   <cols>
     <col min="1" max="1" width="12.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="6" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" style="6" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="6" customWidth="1"/>
     <col min="7" max="7" width="20.7109375" style="6" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" style="8" customWidth="1"/>
   </cols>
@@ -1329,7 +1329,7 @@
         <v>43800</v>
       </c>
       <c r="C13" s="6">
-        <v>93670.15000000001</v>
+        <v>93670.14999999999</v>
       </c>
       <c r="D13" s="6">
         <v>0</v>
@@ -1338,13 +1338,13 @@
         <v>6000</v>
       </c>
       <c r="F13" s="6">
-        <v>93670.15000000001</v>
+        <v>93670.14999999999</v>
       </c>
       <c r="G13" s="6">
         <v>15.61169166666667</v>
       </c>
       <c r="H13" s="8">
-        <v>0.0912325829155447</v>
+        <v>0.09123258291554448</v>
       </c>
     </row>
   </sheetData>
@@ -1628,13 +1628,13 @@
         <v>85838.85000000001</v>
       </c>
       <c r="C5" s="6">
-        <v>93670.15000000001</v>
+        <v>93670.14999999999</v>
       </c>
       <c r="D5" s="6">
-        <v>7831.300000000003</v>
+        <v>7831.299999999988</v>
       </c>
       <c r="E5" s="8">
-        <v>0.0912325829155447</v>
+        <v>0.09123258291554448</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>54</v>
@@ -1648,13 +1648,13 @@
         <v>85838.85000000001</v>
       </c>
       <c r="C6" s="6">
-        <v>93670.15000000001</v>
+        <v>93670.14999999999</v>
       </c>
       <c r="D6" s="6">
-        <v>7831.300000000003</v>
+        <v>7831.299999999988</v>
       </c>
       <c r="E6" s="8">
-        <v>0.0912325829155447</v>
+        <v>0.09123258291554448</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>54</v>
@@ -1709,10 +1709,10 @@
         <v>15.61169166666667</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.05233205596106849</v>
+        <v>-0.05233205596107204</v>
       </c>
       <c r="E9" s="8">
-        <v>-0.003340907603802457</v>
+        <v>-0.003340907603802679</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>56</v>
@@ -1744,10 +1744,10 @@
         <v>-0.03821424109616356</v>
       </c>
       <c r="C11" s="8">
-        <v>0.0912325829155447</v>
+        <v>0.09123258291554448</v>
       </c>
       <c r="D11" s="8">
-        <v>0.1294468240117083</v>
+        <v>0.129446824011708</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="10" t="s">
